--- a/US/May Final/US May Final Data.xlsx
+++ b/US/May Final/US May Final Data.xlsx
@@ -2556,7 +2556,7 @@
     <t>Fulfill social and political responsibilities associated with citizenship in a democratic society and interdependent global community by developing awareness of and/or engaging in the political process.</t>
   </si>
   <si>
-    <t>Kovelsy</t>
+    <t>Kovelsky</t>
   </si>
 </sst>
 </file>
